--- a/excel/PCL_02_Manual_Inputs.xlsx
+++ b/excel/PCL_02_Manual_Inputs.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Inputs!$A$1:$S$156</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1" iterate="false" refMode="A1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="441">
   <si>
     <t xml:space="preserve">File</t>
   </si>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Populated by the lead analyst on 2026-09-28 from Porsche primary documents. Blue = value as printed. Grey = deliberately blank (reason in Note). Label column distinguishes FACT and DERIVED.</t>
+    <t xml:space="preserve">Populated by the lead analyst on 2026-09-28 from Porsche primary documents. Blue = value as printed. Grey = deliberately blank (reason in Note). Label column distinguishes FACT and DERIVED. Source re-check (Oct 2026): rows M095 (X05 FY2023 = 2), M097 (X05 FY2024 = 3) and M143 (O06 FY2023 = 112) filled from the official reports; M099 (X05 FY2025) refined from 1,200 to the exact 1,195. One gap remains (M093, X04 FY2025: not disclosed).</t>
   </si>
   <si>
     <t xml:space="preserve">Rec_ID</t>
@@ -733,7 +733,7 @@
     <t xml:space="preserve">5 and 30</t>
   </si>
   <si>
-    <t xml:space="preserve">Memo, inside X01. Verbatim: 'special expenses of EUR 0.4 billion ... write-downs of production facilities'. S009 slide 28 sub-split conflicts at 0.1bn level (AF-01).</t>
+    <t xml:space="preserve">Memo, inside X01. Verbatim: 'special expenses of EUR 0.4 billion ... write-downs of production facilities'. S009 slide 28 sub-split conflicts at 0.1bn level (AF-01). | Note (Oct 2026): S009 slide 28 shows battery activities 0.5 (with realignment 0.2 and tariffs 0.4, total app. 1.1). The half-year report wording (0.4) is kept; the memo is not used in any KPI.</t>
   </si>
   <si>
     <t xml:space="preserve">Memo: already inside X01</t>
@@ -799,13 +799,13 @@
     <t xml:space="preserve">S012</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD</t>
+    <t xml:space="preserve">Searched: full document (247 PDF pages)</t>
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">BLANK: no FY2025 provision-release amount found in S011/S013/S015; S012 notes could not be parsed remotely. Not estimated.</t>
+    <t xml:space="preserve">BLANK: not disclosed. Source re-check Oct 2026 (official PDF text layer read in full). All 44 mentions of "realignment" in S012 checked: no realignment provision release is stated; only generic totals (provision reversals 276, provisions table; income from reversal of provisions and accruals 97, other operating income note). Not estimated.</t>
   </si>
   <si>
     <t xml:space="preserve">Leave blank if not disclosed; write 'not disclosed' in Note</t>
@@ -838,7 +838,10 @@
     <t xml:space="preserve">S004</t>
   </si>
   <si>
-    <t xml:space="preserve">BLANK: automotive impairment amount for FY2023 not located; annual report S004 could not be parsed remotely. Not estimated.</t>
+    <t xml:space="preserve">Segment reporting table, PDF p.153 (printed pp.304-305)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbatim (segment reporting 2023, row "Impairment losses"): "2 160 162" = automotive 2, financial services 160, total 162. Source re-check Oct 2026 (official PDF text layer read in full). Previously recorded as a gap.</t>
   </si>
   <si>
     <t xml:space="preserve">Search impairment note</t>
@@ -862,7 +865,10 @@
     <t xml:space="preserve">S008</t>
   </si>
   <si>
-    <t xml:space="preserve">BLANK: FY2024 automotive impairment amount not located; S008 could not be parsed remotely. Not estimated.</t>
+    <t xml:space="preserve">Segment reporting table, PDF p.189 (printed p.30 of the financial statements)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbatim (segment reporting 2024, row "Impairment losses"): "3 207 210" = automotive 3, financial services 207, total 210. Source re-check Oct 2026 (official PDF text layer read in full). Previously recorded as a gap.</t>
   </si>
   <si>
     <t xml:space="preserve">M098</t>
@@ -880,13 +886,13 @@
     <t xml:space="preserve">M099</t>
   </si>
   <si>
-    <t xml:space="preserve">34 (footnote)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 100m (text says 'around')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbatim footnote: 'Includes around EUR 1,200 mn of impairment losses due to the strategic realignment'</t>
+    <t xml:space="preserve">Segment reporting table, PDF p.176 (printed p.33 of the financial statements)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S011 p.34 footnote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbatim (segment reporting 2025, row "Impairment losses"): "1,195 250 1,446" = automotive 1,195. S011 slide 34 footnote rounds this as "Includes around EUR 1,200 mn of impairment losses due to the strategic realignment". Source re-check Oct 2026 (official PDF text layer read in full). Value changed from 1,200 (rounded) to 1,195 (exact).</t>
   </si>
   <si>
     <t xml:space="preserve">'around 1,200' -&gt; enter 1200, rounding EUR 100m</t>
@@ -1168,10 +1174,13 @@
     <t xml:space="preserve">M143</t>
   </si>
   <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLANK: Porsche did not publish revenue per vehicle SOLD for FY2023 in the documents reviewed; S003 slide 56 and S007 slide 66 show revenue per DELIVERY (117). DERIVED ASP will be computed in the model (A01 / O04).</t>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbatim: S007 slide 69 "Automotive Sales Revenue per vehicle sold, in EUR k" shows 110 / 112 / 117 for 2022 / 2023 / 2024 (paired by position on the slide). Cross-check: A01 37,349 / vehicle sales 333,605 = 111.96k. S003 slide 56 and S007 slide 66 show revenue per DELIVERY (117). Source re-check Oct 2026 (official PDF text layer read in full). Previously recorded as a gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V1: verbatim quote from the document text (pairing by position), confirmed by A01 / vehicle sales</t>
   </si>
   <si>
     <t xml:space="preserve">M144</t>
@@ -1478,7 +1487,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1528,10 +1537,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1971,7 +1976,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7688,16 +7693,18 @@
         <v>269</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I96" s="8"/>
-      <c r="J96" s="5" t="str">
+      <c r="I96" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="5" t="n">
         <f aca="false">IF(I96="","",IF(H96="EUR bn",I96*1000,I96))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K96" s="5" t="str">
         <f aca="false">IF(H96="EUR bn","EUR m",H96)</f>
@@ -7713,25 +7720,25 @@
         <v>51</v>
       </c>
       <c r="O96" s="7" t="s">
-        <v>258</v>
+        <v>52</v>
       </c>
       <c r="P96" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q96" s="5" t="str">
         <f aca="false">B96&amp;"|"&amp;D96</f>
         <v>X05|FY_2023</v>
       </c>
       <c r="R96" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S96" s="5" t="s">
-        <v>261</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>263</v>
@@ -7746,7 +7753,7 @@
         <v>62</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5" t="s">
@@ -7776,14 +7783,14 @@
         <v>52</v>
       </c>
       <c r="P97" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q97" s="5" t="str">
         <f aca="false">B97&amp;"|"&amp;D97</f>
         <v>X05|H1_2024</v>
       </c>
       <c r="R97" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="S97" s="5" t="s">
         <v>54</v>
@@ -7791,7 +7798,7 @@
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>263</v>
@@ -7803,19 +7810,21 @@
         <v>66</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I98" s="8"/>
-      <c r="J98" s="5" t="str">
+      <c r="I98" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" s="5" t="n">
         <f aca="false">IF(I98="","",IF(H98="EUR bn",I98*1000,I98))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K98" s="5" t="str">
         <f aca="false">IF(H98="EUR bn","EUR m",H98)</f>
@@ -7831,25 +7840,25 @@
         <v>51</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>258</v>
+        <v>52</v>
       </c>
       <c r="P98" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q98" s="5" t="str">
         <f aca="false">B98&amp;"|"&amp;D98</f>
         <v>X05|FY_2024</v>
       </c>
       <c r="R98" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S98" s="5" t="s">
-        <v>261</v>
+        <v>54</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>263</v>
@@ -7864,7 +7873,7 @@
         <v>71</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5" t="s">
@@ -7894,14 +7903,14 @@
         <v>52</v>
       </c>
       <c r="P99" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q99" s="5" t="str">
         <f aca="false">B99&amp;"|"&amp;D99</f>
         <v>X05|H1_2025</v>
       </c>
       <c r="R99" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="S99" s="5" t="s">
         <v>54</v>
@@ -7909,7 +7918,7 @@
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>263</v>
@@ -7921,21 +7930,23 @@
         <v>75</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>122</v>
+        <v>256</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G100" s="5"/>
+        <v>286</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="H100" s="5" t="s">
         <v>48</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="J100" s="5" t="n">
         <f aca="false">IF(I100="","",IF(H100="EUR bn",I100*1000,I100))</f>
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="K100" s="5" t="str">
         <f aca="false">IF(H100="EUR bn","EUR m",H100)</f>
@@ -7945,7 +7956,7 @@
         <v>49</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>285</v>
+        <v>50</v>
       </c>
       <c r="N100" s="7" t="s">
         <v>51</v>
@@ -7954,14 +7965,14 @@
         <v>52</v>
       </c>
       <c r="P100" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q100" s="5" t="str">
         <f aca="false">B100&amp;"|"&amp;D100</f>
         <v>X05|FY_2025</v>
       </c>
       <c r="R100" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S100" s="5" t="s">
         <v>54</v>
@@ -7969,7 +7980,7 @@
     </row>
     <row r="101" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>263</v>
@@ -7984,7 +7995,7 @@
         <v>80</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5" t="s">
@@ -8014,28 +8025,28 @@
         <v>160</v>
       </c>
       <c r="P101" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q101" s="5" t="str">
         <f aca="false">B101&amp;"|"&amp;D101</f>
         <v>X05|H1_2026</v>
       </c>
       <c r="R101" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="S101" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>44</v>
@@ -8044,7 +8055,7 @@
         <v>45</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5" t="s">
@@ -8087,13 +8098,13 @@
     </row>
     <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B103" s="5" t="s">
-        <v>294</v>
-      </c>
       <c r="C103" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>56</v>
@@ -8102,7 +8113,7 @@
         <v>57</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5" t="s">
@@ -8145,13 +8156,13 @@
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>61</v>
@@ -8160,7 +8171,7 @@
         <v>62</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5" t="s">
@@ -8203,13 +8214,13 @@
     </row>
     <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>66</v>
@@ -8218,7 +8229,7 @@
         <v>76</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5" t="s">
@@ -8261,13 +8272,13 @@
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>70</v>
@@ -8276,7 +8287,7 @@
         <v>71</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5" t="s">
@@ -8319,13 +8330,13 @@
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>75</v>
@@ -8334,7 +8345,7 @@
         <v>76</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5" t="s">
@@ -8377,13 +8388,13 @@
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>79</v>
@@ -8392,7 +8403,7 @@
         <v>80</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5" t="s">
@@ -8435,13 +8446,13 @@
     </row>
     <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>44</v>
@@ -8450,10 +8461,10 @@
         <v>45</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>48</v>
@@ -8495,13 +8506,13 @@
     </row>
     <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>309</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>56</v>
@@ -8510,10 +8521,10 @@
         <v>57</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>48</v>
@@ -8555,13 +8566,13 @@
     </row>
     <row r="111" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>61</v>
@@ -8570,10 +8581,10 @@
         <v>62</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>48</v>
@@ -8615,13 +8626,13 @@
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>66</v>
@@ -8630,10 +8641,10 @@
         <v>76</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>48</v>
@@ -8675,13 +8686,13 @@
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>70</v>
@@ -8690,10 +8701,10 @@
         <v>71</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>48</v>
@@ -8735,13 +8746,13 @@
     </row>
     <row r="114" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>75</v>
@@ -8750,10 +8761,10 @@
         <v>76</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>48</v>
@@ -8795,13 +8806,13 @@
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>79</v>
@@ -8810,10 +8821,10 @@
         <v>80</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>48</v>
@@ -8855,22 +8866,22 @@
     </row>
     <row r="116" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5" t="s">
@@ -8900,28 +8911,28 @@
         <v>52</v>
       </c>
       <c r="P116" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q116" s="5" t="str">
         <f aca="false">B116&amp;"|"&amp;D116</f>
         <v>B01|FY_2023</v>
       </c>
       <c r="R116" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S116" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>61</v>
@@ -8930,7 +8941,7 @@
         <v>158</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5" t="s">
@@ -8951,7 +8962,7 @@
         <v>49</v>
       </c>
       <c r="M117" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N117" s="7" t="s">
         <v>51</v>
@@ -8960,37 +8971,37 @@
         <v>52</v>
       </c>
       <c r="P117" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q117" s="5" t="str">
         <f aca="false">B117&amp;"|"&amp;D117</f>
         <v>B01|H1_2024</v>
       </c>
       <c r="R117" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S117" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5" t="s">
@@ -9020,37 +9031,37 @@
         <v>52</v>
       </c>
       <c r="P118" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q118" s="5" t="str">
         <f aca="false">B118&amp;"|"&amp;D118</f>
         <v>B01|FY_2024</v>
       </c>
       <c r="R118" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S118" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5" t="s">
@@ -9071,7 +9082,7 @@
         <v>49</v>
       </c>
       <c r="M119" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N119" s="7" t="s">
         <v>51</v>
@@ -9080,28 +9091,28 @@
         <v>52</v>
       </c>
       <c r="P119" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q119" s="5" t="str">
         <f aca="false">B119&amp;"|"&amp;D119</f>
         <v>B01|H1_2025</v>
       </c>
       <c r="R119" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S119" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>75</v>
@@ -9131,7 +9142,7 @@
         <v>49</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N120" s="7" t="s">
         <v>51</v>
@@ -9140,28 +9151,28 @@
         <v>52</v>
       </c>
       <c r="P120" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q120" s="5" t="str">
         <f aca="false">B120&amp;"|"&amp;D120</f>
         <v>B01|FY_2025</v>
       </c>
       <c r="R120" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S120" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>79</v>
@@ -9191,7 +9202,7 @@
         <v>49</v>
       </c>
       <c r="M121" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N121" s="7" t="s">
         <v>51</v>
@@ -9200,37 +9211,37 @@
         <v>52</v>
       </c>
       <c r="P121" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q121" s="5" t="str">
         <f aca="false">B121&amp;"|"&amp;D121</f>
         <v>B01|H1_2026</v>
       </c>
       <c r="R121" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S121" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5" t="s">
@@ -9260,28 +9271,28 @@
         <v>52</v>
       </c>
       <c r="P122" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q122" s="5" t="str">
         <f aca="false">B122&amp;"|"&amp;D122</f>
         <v>B02|FY_2023</v>
       </c>
       <c r="R122" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S122" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B123" s="5" t="s">
-        <v>338</v>
-      </c>
       <c r="C123" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>61</v>
@@ -9290,7 +9301,7 @@
         <v>158</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5" t="s">
@@ -9311,7 +9322,7 @@
         <v>49</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N123" s="7" t="s">
         <v>51</v>
@@ -9320,37 +9331,37 @@
         <v>52</v>
       </c>
       <c r="P123" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q123" s="5" t="str">
         <f aca="false">B123&amp;"|"&amp;D123</f>
         <v>B02|H1_2024</v>
       </c>
       <c r="R123" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S123" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C124" s="5" t="s">
         <v>341</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>339</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5" t="s">
@@ -9380,37 +9391,37 @@
         <v>52</v>
       </c>
       <c r="P124" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q124" s="5" t="str">
         <f aca="false">B124&amp;"|"&amp;D124</f>
         <v>B02|FY_2024</v>
       </c>
       <c r="R124" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S124" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5" t="s">
@@ -9431,7 +9442,7 @@
         <v>49</v>
       </c>
       <c r="M125" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N125" s="7" t="s">
         <v>51</v>
@@ -9440,28 +9451,28 @@
         <v>52</v>
       </c>
       <c r="P125" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q125" s="5" t="str">
         <f aca="false">B125&amp;"|"&amp;D125</f>
         <v>B02|H1_2025</v>
       </c>
       <c r="R125" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S125" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>75</v>
@@ -9491,7 +9502,7 @@
         <v>49</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N126" s="7" t="s">
         <v>51</v>
@@ -9500,28 +9511,28 @@
         <v>52</v>
       </c>
       <c r="P126" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q126" s="5" t="str">
         <f aca="false">B126&amp;"|"&amp;D126</f>
         <v>B02|FY_2025</v>
       </c>
       <c r="R126" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S126" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>79</v>
@@ -9551,7 +9562,7 @@
         <v>49</v>
       </c>
       <c r="M127" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N127" s="7" t="s">
         <v>51</v>
@@ -9560,37 +9571,37 @@
         <v>52</v>
       </c>
       <c r="P127" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q127" s="5" t="str">
         <f aca="false">B127&amp;"|"&amp;D127</f>
         <v>B02|H1_2026</v>
       </c>
       <c r="R127" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S127" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5" t="s">
@@ -9620,28 +9631,28 @@
         <v>52</v>
       </c>
       <c r="P128" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q128" s="5" t="str">
         <f aca="false">B128&amp;"|"&amp;D128</f>
         <v>B03|FY_2023</v>
       </c>
       <c r="R128" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S128" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B129" s="5" t="s">
-        <v>346</v>
-      </c>
       <c r="C129" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>61</v>
@@ -9650,7 +9661,7 @@
         <v>158</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5" t="s">
@@ -9671,7 +9682,7 @@
         <v>49</v>
       </c>
       <c r="M129" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N129" s="7" t="s">
         <v>51</v>
@@ -9680,37 +9691,37 @@
         <v>52</v>
       </c>
       <c r="P129" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q129" s="5" t="str">
         <f aca="false">B129&amp;"|"&amp;D129</f>
         <v>B03|H1_2024</v>
       </c>
       <c r="R129" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S129" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5" t="s">
@@ -9740,37 +9751,37 @@
         <v>52</v>
       </c>
       <c r="P130" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q130" s="5" t="str">
         <f aca="false">B130&amp;"|"&amp;D130</f>
         <v>B03|FY_2024</v>
       </c>
       <c r="R130" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S130" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5" t="s">
@@ -9791,7 +9802,7 @@
         <v>49</v>
       </c>
       <c r="M131" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N131" s="7" t="s">
         <v>51</v>
@@ -9800,28 +9811,28 @@
         <v>52</v>
       </c>
       <c r="P131" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q131" s="5" t="str">
         <f aca="false">B131&amp;"|"&amp;D131</f>
         <v>B03|H1_2025</v>
       </c>
       <c r="R131" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S131" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>75</v>
@@ -9851,7 +9862,7 @@
         <v>49</v>
       </c>
       <c r="M132" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N132" s="7" t="s">
         <v>51</v>
@@ -9860,28 +9871,28 @@
         <v>52</v>
       </c>
       <c r="P132" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q132" s="5" t="str">
         <f aca="false">B132&amp;"|"&amp;D132</f>
         <v>B03|FY_2025</v>
       </c>
       <c r="R132" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S132" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>79</v>
@@ -9911,7 +9922,7 @@
         <v>49</v>
       </c>
       <c r="M133" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N133" s="7" t="s">
         <v>51</v>
@@ -9920,37 +9931,37 @@
         <v>52</v>
       </c>
       <c r="P133" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q133" s="5" t="str">
         <f aca="false">B133&amp;"|"&amp;D133</f>
         <v>B03|H1_2026</v>
       </c>
       <c r="R133" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S133" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5" t="s">
@@ -9980,28 +9991,28 @@
         <v>52</v>
       </c>
       <c r="P134" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q134" s="5" t="str">
         <f aca="false">B134&amp;"|"&amp;D134</f>
         <v>B04|FY_2023</v>
       </c>
       <c r="R134" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S134" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>354</v>
-      </c>
       <c r="C135" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>61</v>
@@ -10010,7 +10021,7 @@
         <v>158</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5" t="s">
@@ -10031,7 +10042,7 @@
         <v>49</v>
       </c>
       <c r="M135" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N135" s="7" t="s">
         <v>51</v>
@@ -10040,37 +10051,37 @@
         <v>52</v>
       </c>
       <c r="P135" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q135" s="5" t="str">
         <f aca="false">B135&amp;"|"&amp;D135</f>
         <v>B04|H1_2024</v>
       </c>
       <c r="R135" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S135" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>357</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5" t="s">
@@ -10100,37 +10111,37 @@
         <v>52</v>
       </c>
       <c r="P136" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q136" s="5" t="str">
         <f aca="false">B136&amp;"|"&amp;D136</f>
         <v>B04|FY_2024</v>
       </c>
       <c r="R136" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S136" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5" t="s">
@@ -10151,7 +10162,7 @@
         <v>49</v>
       </c>
       <c r="M137" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N137" s="7" t="s">
         <v>51</v>
@@ -10160,28 +10171,28 @@
         <v>52</v>
       </c>
       <c r="P137" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q137" s="5" t="str">
         <f aca="false">B137&amp;"|"&amp;D137</f>
         <v>B04|H1_2025</v>
       </c>
       <c r="R137" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S137" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>75</v>
@@ -10211,7 +10222,7 @@
         <v>49</v>
       </c>
       <c r="M138" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N138" s="7" t="s">
         <v>51</v>
@@ -10220,28 +10231,28 @@
         <v>52</v>
       </c>
       <c r="P138" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q138" s="5" t="str">
         <f aca="false">B138&amp;"|"&amp;D138</f>
         <v>B04|FY_2025</v>
       </c>
       <c r="R138" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S138" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>79</v>
@@ -10271,7 +10282,7 @@
         <v>49</v>
       </c>
       <c r="M139" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N139" s="7" t="s">
         <v>51</v>
@@ -10280,37 +10291,37 @@
         <v>52</v>
       </c>
       <c r="P139" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q139" s="5" t="str">
         <f aca="false">B139&amp;"|"&amp;D139</f>
         <v>B04|H1_2026</v>
       </c>
       <c r="R139" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S139" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5" t="s">
@@ -10331,7 +10342,7 @@
         <v>49</v>
       </c>
       <c r="M140" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N140" s="7" t="s">
         <v>51</v>
@@ -10340,14 +10351,14 @@
         <v>52</v>
       </c>
       <c r="P140" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q140" s="5" t="str">
         <f aca="false">B140&amp;"|"&amp;D140</f>
         <v>B05|H1_2025</v>
       </c>
       <c r="R140" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S140" s="5" t="s">
         <v>54</v>
@@ -10355,13 +10366,13 @@
     </row>
     <row r="141" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>75</v>
@@ -10400,14 +10411,14 @@
         <v>52</v>
       </c>
       <c r="P141" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q141" s="5" t="str">
         <f aca="false">B141&amp;"|"&amp;D141</f>
         <v>B05|FY_2025</v>
       </c>
       <c r="R141" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S141" s="5" t="s">
         <v>54</v>
@@ -10415,13 +10426,13 @@
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>79</v>
@@ -10460,14 +10471,14 @@
         <v>52</v>
       </c>
       <c r="P142" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q142" s="5" t="str">
         <f aca="false">B142&amp;"|"&amp;D142</f>
         <v>B05|H1_2026</v>
       </c>
       <c r="R142" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S142" s="5" t="s">
         <v>54</v>
@@ -10475,13 +10486,13 @@
     </row>
     <row r="143" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>44</v>
@@ -10490,11 +10501,11 @@
         <v>158</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I143" s="6" t="n">
         <v>111</v>
@@ -10511,7 +10522,7 @@
         <v>49</v>
       </c>
       <c r="M143" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N143" s="7" t="s">
         <v>51</v>
@@ -10520,46 +10531,48 @@
         <v>52</v>
       </c>
       <c r="P143" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q143" s="5" t="str">
         <f aca="false">B143&amp;"|"&amp;D143</f>
         <v>O06|H1_2023</v>
       </c>
       <c r="R143" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S143" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="I144" s="8"/>
-      <c r="J144" s="5" t="str">
+        <v>376</v>
+      </c>
+      <c r="I144" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="J144" s="5" t="n">
         <f aca="false">IF(I144="","",IF(H144="EUR bn",I144*1000,I144))</f>
-        <v/>
+        <v>112</v>
       </c>
       <c r="K144" s="5" t="str">
         <f aca="false">IF(H144="EUR bn","EUR m",H144)</f>
@@ -10569,50 +10582,50 @@
         <v>49</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N144" s="7" t="s">
         <v>51</v>
       </c>
       <c r="O144" s="7" t="s">
-        <v>258</v>
+        <v>52</v>
       </c>
       <c r="P144" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q144" s="5" t="str">
         <f aca="false">B144&amp;"|"&amp;D144</f>
         <v>O06|FY_2023</v>
       </c>
       <c r="R144" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S144" s="5" t="s">
-        <v>261</v>
+        <v>384</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I145" s="6" t="n">
         <v>116</v>
@@ -10629,7 +10642,7 @@
         <v>49</v>
       </c>
       <c r="M145" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N145" s="7" t="s">
         <v>51</v>
@@ -10645,7 +10658,7 @@
         <v>O06|H1_2024</v>
       </c>
       <c r="R145" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S145" s="5" t="s">
         <v>54</v>
@@ -10653,13 +10666,13 @@
     </row>
     <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>66</v>
@@ -10668,11 +10681,11 @@
         <v>122</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I146" s="6" t="n">
         <v>117</v>
@@ -10689,7 +10702,7 @@
         <v>49</v>
       </c>
       <c r="M146" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N146" s="7" t="s">
         <v>51</v>
@@ -10705,7 +10718,7 @@
         <v>O06|FY_2024</v>
       </c>
       <c r="R146" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S146" s="5" t="s">
         <v>54</v>
@@ -10713,13 +10726,13 @@
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>70</v>
@@ -10728,11 +10741,11 @@
         <v>126</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I147" s="6" t="n">
         <v>119</v>
@@ -10749,7 +10762,7 @@
         <v>49</v>
       </c>
       <c r="M147" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N147" s="7" t="s">
         <v>51</v>
@@ -10758,14 +10771,14 @@
         <v>52</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q147" s="5" t="str">
         <f aca="false">B147&amp;"|"&amp;D147</f>
         <v>O06|H1_2025</v>
       </c>
       <c r="R147" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S147" s="5" t="s">
         <v>54</v>
@@ -10773,13 +10786,13 @@
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="5" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>75</v>
@@ -10788,11 +10801,11 @@
         <v>122</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I148" s="6" t="n">
         <v>121</v>
@@ -10809,7 +10822,7 @@
         <v>49</v>
       </c>
       <c r="M148" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N148" s="7" t="s">
         <v>51</v>
@@ -10825,7 +10838,7 @@
         <v>O06|FY_2025</v>
       </c>
       <c r="R148" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S148" s="5" t="s">
         <v>54</v>
@@ -10833,13 +10846,13 @@
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>79</v>
@@ -10848,11 +10861,11 @@
         <v>126</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I149" s="6" t="n">
         <v>126</v>
@@ -10869,7 +10882,7 @@
         <v>49</v>
       </c>
       <c r="M149" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N149" s="7" t="s">
         <v>51</v>
@@ -10885,7 +10898,7 @@
         <v>O06|H1_2026</v>
       </c>
       <c r="R149" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S149" s="5" t="s">
         <v>54</v>
@@ -10893,13 +10906,13 @@
     </row>
     <row r="150" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>44</v>
@@ -10908,7 +10921,7 @@
         <v>62</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G150" s="5"/>
       <c r="H150" s="5" t="s">
@@ -10938,14 +10951,14 @@
         <v>52</v>
       </c>
       <c r="P150" s="7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q150" s="5" t="str">
         <f aca="false">B150&amp;"|"&amp;D150</f>
         <v>O07|H1_2023</v>
       </c>
       <c r="R150" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S150" s="5" t="s">
         <v>54</v>
@@ -10953,22 +10966,22 @@
     </row>
     <row r="151" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5" t="s">
@@ -10998,28 +11011,28 @@
         <v>160</v>
       </c>
       <c r="P151" s="7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q151" s="5" t="str">
         <f aca="false">B151&amp;"|"&amp;D151</f>
         <v>O07|FY_2023</v>
       </c>
       <c r="R151" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S151" s="5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>61</v>
@@ -11028,7 +11041,7 @@
         <v>62</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5" t="s">
@@ -11058,14 +11071,14 @@
         <v>52</v>
       </c>
       <c r="P152" s="7" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q152" s="5" t="str">
         <f aca="false">B152&amp;"|"&amp;D152</f>
         <v>O07|H1_2024</v>
       </c>
       <c r="R152" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S152" s="5" t="s">
         <v>54</v>
@@ -11073,13 +11086,13 @@
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>66</v>
@@ -11088,7 +11101,7 @@
         <v>122</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5" t="s">
@@ -11118,14 +11131,14 @@
         <v>52</v>
       </c>
       <c r="P153" s="7" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q153" s="5" t="str">
         <f aca="false">B153&amp;"|"&amp;D153</f>
         <v>O07|FY_2024</v>
       </c>
       <c r="R153" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S153" s="5" t="s">
         <v>54</v>
@@ -11133,13 +11146,13 @@
     </row>
     <row r="154" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>70</v>
@@ -11148,7 +11161,7 @@
         <v>71</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5" t="s">
@@ -11185,7 +11198,7 @@
         <v>O07|H1_2025</v>
       </c>
       <c r="R154" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S154" s="5" t="s">
         <v>54</v>
@@ -11193,13 +11206,13 @@
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>75</v>
@@ -11208,7 +11221,7 @@
         <v>122</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5" t="s">
@@ -11238,14 +11251,14 @@
         <v>52</v>
       </c>
       <c r="P155" s="7" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q155" s="5" t="str">
         <f aca="false">B155&amp;"|"&amp;D155</f>
         <v>O07|FY_2025</v>
       </c>
       <c r="R155" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S155" s="5" t="s">
         <v>54</v>
@@ -11253,13 +11266,13 @@
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>79</v>
@@ -11268,7 +11281,7 @@
         <v>80</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5" t="s">
@@ -11305,7 +11318,7 @@
         <v>O07|H1_2026</v>
       </c>
       <c r="R156" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="S156" s="5" t="s">
         <v>54</v>
@@ -11354,33 +11367,33 @@
         <v>25</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>17921.7</v>
@@ -11395,7 +11408,7 @@
         <v>145860</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>5053.6</v>
@@ -11409,7 +11422,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>37637.4</v>
@@ -11424,7 +11437,7 @@
         <v>309884</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>10548.6</v>
@@ -11453,7 +11466,7 @@
         <v>167354</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>5909.4</v>
@@ -11482,7 +11495,7 @@
         <v>320221</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>11605.9</v>
@@ -11511,7 +11524,7 @@
         <v>155945</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>5206</v>
@@ -11540,7 +11553,7 @@
         <v>310718</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>10327.4</v>
@@ -11569,7 +11582,7 @@
         <v>146391</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>3363.9</v>
@@ -11598,7 +11611,7 @@
         <v>279449</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>5050.9</v>
@@ -11627,7 +11640,7 @@
         <v>122306</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>3465.8</v>
@@ -11667,46 +11680,46 @@
         <v>25</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11795,7 +11808,7 @@
       </c>
       <c r="G3" s="3" t="str">
         <f aca="false">IF((COUNTIFS(Inputs!$Q$2:$Q$156,"A01|"&amp;$A3,Inputs!$I$2:$I$156,"&lt;&gt;"))*(COUNTIFS(Inputs!$Q$2:$Q$156,"O06|"&amp;$A3,Inputs!$I$2:$I$156,"&lt;&gt;"))=0,IF(COUNTIFS(Inputs!$Q$2:$Q$156,"O06|"&amp;$A3,Inputs!$I$2:$I$156,"",Inputs!$P$2:$P$156,"&lt;&gt;")&gt;0,"N/A (blank - see Inputs note)","PENDING"),IF(ABS(SUMIFS(Inputs!$J$2:$J$156,Inputs!$Q$2:$Q$156,"A01|"&amp;$A3)*1000/INDEX(FS_Reference!$D$2:$D$10,MATCH($A3,FS_Reference!$A$2:$A$10,0))-SUMIFS(Inputs!$J$2:$J$156,Inputs!$Q$2:$Q$156,"O06|"&amp;$A3))&lt;=1.5,"OK","CHECK"))</f>
-        <v>N/A (blank - see Inputs note)</v>
+        <v>OK</v>
       </c>
       <c r="H3" s="3" t="str">
         <f aca="false">IF((COUNTIFS(Inputs!$Q$2:$Q$156,"B01|"&amp;$A3,Inputs!$I$2:$I$156,"&lt;&gt;"))*(COUNTIFS(Inputs!$Q$2:$Q$156,"B02|"&amp;$A3,Inputs!$I$2:$I$156,"&lt;&gt;"))*(COUNTIFS(Inputs!$Q$2:$Q$156,"B03|"&amp;$A3,Inputs!$I$2:$I$156,"&lt;&gt;"))*(COUNTIFS(Inputs!$Q$2:$Q$156,"B04|"&amp;$A3,Inputs!$I$2:$I$156,"&lt;&gt;"))=0,"PENDING",IF(ABS(INDEX(FS_Reference!$C$2:$C$10,MATCH("FY_2022",FS_Reference!$A$2:$A$10,0))+SUMIFS(Inputs!$J$2:$J$156,Inputs!$Q$2:$Q$156,"B01|"&amp;$A3)+SUMIFS(Inputs!$J$2:$J$156,Inputs!$Q$2:$Q$156,"B02|"&amp;$A3)+SUMIFS(Inputs!$J$2:$J$156,Inputs!$Q$2:$Q$156,"B03|"&amp;$A3)+SUMIFS(Inputs!$J$2:$J$156,Inputs!$Q$2:$Q$156,"B04|"&amp;$A3)-INDEX(FS_Reference!$C$2:$C$10,MATCH($A3,FS_Reference!$A$2:$A$10,0)))&lt;=$L3,"OK","CHECK"))</f>
@@ -11818,11 +11831,11 @@
       </c>
       <c r="M3" s="3" t="n">
         <f aca="false">COUNTIFS(Inputs!$D$2:$D$156,$A3,Inputs!$I$2:$I$156,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N3" s="3" t="n">
         <f aca="false">COUNTIFS(Inputs!$D$2:$D$156,$A3,Inputs!$I$2:$I$156,"",Inputs!$P$2:$P$156,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" s="3" t="n">
         <f aca="false">COUNTIFS(Inputs!$D$2:$D$156,$A3)</f>
@@ -11938,11 +11951,11 @@
       </c>
       <c r="M5" s="3" t="n">
         <f aca="false">COUNTIFS(Inputs!$D$2:$D$156,$A5,Inputs!$I$2:$I$156,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" s="3" t="n">
         <f aca="false">COUNTIFS(Inputs!$D$2:$D$156,$A5,Inputs!$I$2:$I$156,"",Inputs!$P$2:$P$156,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
         <f aca="false">COUNTIFS(Inputs!$D$2:$D$156,$A5)</f>
@@ -12131,15 +12144,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M10" s="2" t="n">
         <f aca="false">SUM(M2:M8)</f>
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N10" s="2" t="n">
         <f aca="false">SUM(N2:N8)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2" t="n">
         <f aca="false">SUM(O2:O8)</f>
@@ -12148,41 +12161,41 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="13" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="10" t="n">
         <f aca="false">COUNTIF(Inputs!$O$2:$O$156,"Y")</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="10" t="n">
         <f aca="false">COUNTIF(Inputs!$O$2:$O$156,"N")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="10" t="n">
         <f aca="false">COUNTIF(Inputs!$O$2:$O$156,"N/A")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="B16" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B16" s="10" t="n">
         <f aca="false">SUM(B13:B15)</f>
         <v>155</v>
       </c>
